--- a/statistics_files/2026/2026_99_gc_sharing.xlsx
+++ b/statistics_files/2026/2026_99_gc_sharing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF4DBFF-D719-45C8-A435-470FF614D279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F056BA-3D8E-41CA-8120-C25BC2EE406E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January" sheetId="1" r:id="rId1"/>
@@ -3431,15 +3431,15 @@
       </c>
       <c r="B2" s="3">
         <f>SUM(January:December!B2)</f>
-        <v>31377</v>
+        <v>35781</v>
       </c>
       <c r="C2" s="3">
         <f>SUM(January:December!C2)</f>
-        <v>9925</v>
+        <v>11394</v>
       </c>
       <c r="D2" s="3">
         <f>SUM(January:December!D2)</f>
-        <v>41302</v>
+        <v>47175</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3448,15 +3448,15 @@
       </c>
       <c r="B3" s="4">
         <f>SUM(January:December!B3)</f>
-        <v>20066</v>
+        <v>22925</v>
       </c>
       <c r="C3" s="4">
         <f>SUM(January:December!C3)</f>
-        <v>4490</v>
+        <v>5123</v>
       </c>
       <c r="D3" s="4">
         <f>SUM(January:December!D3)</f>
-        <v>24556</v>
+        <v>28048</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3465,15 +3465,15 @@
       </c>
       <c r="B4" s="3">
         <f>SUM(January:December!B4)</f>
-        <v>55232</v>
+        <v>62917</v>
       </c>
       <c r="C4" s="3">
         <f>SUM(January:December!C4)</f>
-        <v>8337</v>
+        <v>9569</v>
       </c>
       <c r="D4" s="3">
         <f>SUM(January:December!D4)</f>
-        <v>63569</v>
+        <v>72486</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3482,15 +3482,15 @@
       </c>
       <c r="B5" s="4">
         <f>SUM(January:December!B5)</f>
-        <v>1116</v>
+        <v>1264</v>
       </c>
       <c r="C5" s="4">
         <f>SUM(January:December!C5)</f>
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="D5" s="4">
         <f>SUM(January:December!D5)</f>
-        <v>1280</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3499,15 +3499,15 @@
       </c>
       <c r="B6" s="3">
         <f>SUM(January:December!B6)</f>
-        <v>38893</v>
+        <v>44139</v>
       </c>
       <c r="C6" s="3">
         <f>SUM(January:December!C6)</f>
-        <v>6861</v>
+        <v>7768</v>
       </c>
       <c r="D6" s="3">
         <f>SUM(January:December!D6)</f>
-        <v>45754</v>
+        <v>51907</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3516,15 +3516,15 @@
       </c>
       <c r="B7" s="4">
         <f>SUM(January:December!B7)</f>
-        <v>4203</v>
+        <v>4828</v>
       </c>
       <c r="C7" s="4">
         <f>SUM(January:December!C7)</f>
-        <v>1772</v>
+        <v>2028</v>
       </c>
       <c r="D7" s="4">
         <f>SUM(January:December!D7)</f>
-        <v>5975</v>
+        <v>6856</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3533,15 +3533,15 @@
       </c>
       <c r="B8" s="3">
         <f>SUM(January:December!B8)</f>
-        <v>2979</v>
+        <v>3302</v>
       </c>
       <c r="C8" s="3">
         <f>SUM(January:December!C8)</f>
-        <v>801</v>
+        <v>929</v>
       </c>
       <c r="D8" s="3">
         <f>SUM(January:December!D8)</f>
-        <v>3780</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3550,15 +3550,15 @@
       </c>
       <c r="B9" s="4">
         <f>SUM(January:December!B9)</f>
-        <v>1697</v>
+        <v>1979</v>
       </c>
       <c r="C9" s="4">
         <f>SUM(January:December!C9)</f>
-        <v>420</v>
+        <v>514</v>
       </c>
       <c r="D9" s="4">
         <f>SUM(January:December!D9)</f>
-        <v>2117</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="B10" s="3">
         <f>SUM(January:December!B10)</f>
-        <v>377</v>
+        <v>427</v>
       </c>
       <c r="C10" s="3">
         <f>SUM(January:December!C10)</f>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="D10" s="3">
         <f>SUM(January:December!D10)</f>
-        <v>382</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3601,15 +3601,15 @@
       </c>
       <c r="B12" s="5">
         <f>SUM(January:December!B12)</f>
-        <v>232</v>
+        <v>287</v>
       </c>
       <c r="C12" s="5">
         <f>SUM(January:December!C12)</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D12" s="5">
         <f>SUM(January:December!D12)</f>
-        <v>271</v>
+        <v>328</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3618,15 +3618,15 @@
       </c>
       <c r="B13" s="6">
         <f>SUM(January:December!B13)</f>
-        <v>921</v>
+        <v>1082</v>
       </c>
       <c r="C13" s="6">
         <f>SUM(January:December!C13)</f>
-        <v>323</v>
+        <v>349</v>
       </c>
       <c r="D13" s="6">
         <f>SUM(January:December!D13)</f>
-        <v>1244</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3635,15 +3635,15 @@
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>4233</v>
+        <v>4793</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>867</v>
+        <v>979</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>5100</v>
+        <v>5772</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3652,15 +3652,15 @@
       </c>
       <c r="B15" s="6">
         <f>SUM(January:December!B15)</f>
-        <v>1977</v>
+        <v>2238</v>
       </c>
       <c r="C15" s="6">
         <f>SUM(January:December!C15)</f>
-        <v>327</v>
+        <v>379</v>
       </c>
       <c r="D15" s="6">
         <f>SUM(January:December!D15)</f>
-        <v>2304</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3669,15 +3669,15 @@
       </c>
       <c r="B16" s="3">
         <f>SUM(January:December!B16)</f>
-        <v>1713</v>
+        <v>1984</v>
       </c>
       <c r="C16" s="3">
         <f>SUM(January:December!C16)</f>
-        <v>413</v>
+        <v>470</v>
       </c>
       <c r="D16" s="3">
         <f>SUM(January:December!D16)</f>
-        <v>2126</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3686,15 +3686,15 @@
       </c>
       <c r="B17" s="4">
         <f>SUM(January:December!B17)</f>
-        <v>10063</v>
+        <v>11430</v>
       </c>
       <c r="C17" s="4">
         <f>SUM(January:December!C17)</f>
-        <v>4526</v>
+        <v>5246</v>
       </c>
       <c r="D17" s="4">
         <f>SUM(January:December!D17)</f>
-        <v>14589</v>
+        <v>16676</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3703,15 +3703,15 @@
       </c>
       <c r="B18" s="3">
         <f>SUM(January:December!B18)</f>
-        <v>705</v>
+        <v>797</v>
       </c>
       <c r="C18" s="3">
         <f>SUM(January:December!C18)</f>
-        <v>595</v>
+        <v>641</v>
       </c>
       <c r="D18" s="3">
         <f>SUM(January:December!D18)</f>
-        <v>1300</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3720,15 +3720,15 @@
       </c>
       <c r="B19" s="4">
         <f>SUM(January:December!B19)</f>
-        <v>12121</v>
+        <v>13864</v>
       </c>
       <c r="C19" s="4">
         <f>SUM(January:December!C19)</f>
-        <v>3550</v>
+        <v>4034</v>
       </c>
       <c r="D19" s="4">
         <f>SUM(January:December!D19)</f>
-        <v>15671</v>
+        <v>17898</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3737,15 +3737,15 @@
       </c>
       <c r="B20" s="3">
         <f>SUM(January:December!B20)</f>
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="C20" s="3">
         <f>SUM(January:December!C20)</f>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D20" s="3">
         <f>SUM(January:December!D20)</f>
-        <v>142</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3754,15 +3754,15 @@
       </c>
       <c r="B21" s="4">
         <f>SUM(January:December!B21)</f>
-        <v>11134</v>
+        <v>12845</v>
       </c>
       <c r="C21" s="4">
         <f>SUM(January:December!C21)</f>
-        <v>3481</v>
+        <v>3976</v>
       </c>
       <c r="D21" s="4">
         <f>SUM(January:December!D21)</f>
-        <v>14615</v>
+        <v>16821</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3771,15 +3771,15 @@
       </c>
       <c r="B22" s="3">
         <f>SUM(January:December!B22)</f>
-        <v>2046</v>
+        <v>2276</v>
       </c>
       <c r="C22" s="3">
         <f>SUM(January:December!C22)</f>
-        <v>586</v>
+        <v>659</v>
       </c>
       <c r="D22" s="3">
         <f>SUM(January:December!D22)</f>
-        <v>2632</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3788,15 +3788,15 @@
       </c>
       <c r="B23" s="4">
         <f>SUM(January:December!B23)</f>
-        <v>15807</v>
+        <v>18266</v>
       </c>
       <c r="C23" s="4">
         <f>SUM(January:December!C23)</f>
-        <v>4489</v>
+        <v>5286</v>
       </c>
       <c r="D23" s="4">
         <f>SUM(January:December!D23)</f>
-        <v>20296</v>
+        <v>23552</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3805,15 +3805,15 @@
       </c>
       <c r="B24" s="3">
         <f>SUM(January:December!B24)</f>
-        <v>74704</v>
+        <v>86643</v>
       </c>
       <c r="C24" s="3">
         <f>SUM(January:December!C24)</f>
-        <v>12206</v>
+        <v>13971</v>
       </c>
       <c r="D24" s="3">
         <f>SUM(January:December!D24)</f>
-        <v>86910</v>
+        <v>100614</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3822,15 +3822,15 @@
       </c>
       <c r="B25" s="4">
         <f>SUM(January:December!B25)</f>
-        <v>3152</v>
+        <v>3747</v>
       </c>
       <c r="C25" s="4">
         <f>SUM(January:December!C25)</f>
-        <v>1055</v>
+        <v>1215</v>
       </c>
       <c r="D25" s="4">
         <f>SUM(January:December!D25)</f>
-        <v>4207</v>
+        <v>4962</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3856,15 +3856,15 @@
       </c>
       <c r="B27" s="4">
         <f>SUM(January:December!B27)</f>
-        <v>3241</v>
+        <v>3611</v>
       </c>
       <c r="C27" s="4">
         <f>SUM(January:December!C27)</f>
-        <v>1448</v>
+        <v>1639</v>
       </c>
       <c r="D27" s="4">
         <f>SUM(January:December!D27)</f>
-        <v>4689</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3873,15 +3873,15 @@
       </c>
       <c r="B28" s="3">
         <f>SUM(January:December!B28)</f>
-        <v>2336</v>
+        <v>2629</v>
       </c>
       <c r="C28" s="3">
         <f>SUM(January:December!C28)</f>
-        <v>1052</v>
+        <v>1235</v>
       </c>
       <c r="D28" s="3">
         <f>SUM(January:December!D28)</f>
-        <v>3388</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3890,15 +3890,15 @@
       </c>
       <c r="B29" s="4">
         <f>SUM(January:December!B29)</f>
-        <v>15015</v>
+        <v>16482</v>
       </c>
       <c r="C29" s="4">
         <f>SUM(January:December!C29)</f>
-        <v>5853</v>
+        <v>6567</v>
       </c>
       <c r="D29" s="4">
         <f>SUM(January:December!D29)</f>
-        <v>20868</v>
+        <v>23049</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3907,15 +3907,15 @@
       </c>
       <c r="B30" s="3">
         <f>SUM(January:December!B30)</f>
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="C30" s="3">
         <f>SUM(January:December!C30)</f>
-        <v>263</v>
+        <v>299</v>
       </c>
       <c r="D30" s="3">
         <f>SUM(January:December!D30)</f>
-        <v>348</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3924,15 +3924,15 @@
       </c>
       <c r="B31" s="4">
         <f>SUM(January:December!B31)</f>
-        <v>2132</v>
+        <v>2275</v>
       </c>
       <c r="C31" s="4">
         <f>SUM(January:December!C31)</f>
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="D31" s="4">
         <f>SUM(January:December!D31)</f>
-        <v>2935</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3941,15 +3941,15 @@
       </c>
       <c r="B32" s="3">
         <f>SUM(January:December!B32)</f>
-        <v>9573</v>
+        <v>10989</v>
       </c>
       <c r="C32" s="3">
         <f>SUM(January:December!C32)</f>
-        <v>2825</v>
+        <v>3264</v>
       </c>
       <c r="D32" s="3">
         <f>SUM(January:December!D32)</f>
-        <v>12398</v>
+        <v>14253</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3958,15 +3958,15 @@
       </c>
       <c r="B33" s="4">
         <f>SUM(January:December!B33)</f>
-        <v>6628</v>
+        <v>7599</v>
       </c>
       <c r="C33" s="4">
         <f>SUM(January:December!C33)</f>
-        <v>2419</v>
+        <v>2785</v>
       </c>
       <c r="D33" s="4">
         <f>SUM(January:December!D33)</f>
-        <v>9047</v>
+        <v>10384</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3975,15 +3975,15 @@
       </c>
       <c r="B34" s="3">
         <f>SUM(January:December!B34)</f>
-        <v>3476</v>
+        <v>4069</v>
       </c>
       <c r="C34" s="3">
         <f>SUM(January:December!C34)</f>
-        <v>1197</v>
+        <v>1375</v>
       </c>
       <c r="D34" s="3">
         <f>SUM(January:December!D34)</f>
-        <v>4673</v>
+        <v>5444</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3992,15 +3992,15 @@
       </c>
       <c r="B35" s="4">
         <f>SUM(January:December!B35)</f>
-        <v>39622</v>
+        <v>45680</v>
       </c>
       <c r="C35" s="4">
         <f>SUM(January:December!C35)</f>
-        <v>6946</v>
+        <v>8164</v>
       </c>
       <c r="D35" s="4">
         <f>SUM(January:December!D35)</f>
-        <v>46568</v>
+        <v>53844</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4009,15 +4009,15 @@
       </c>
       <c r="B36" s="3">
         <f>SUM(January:December!B36)</f>
-        <v>5650</v>
+        <v>6337</v>
       </c>
       <c r="C36" s="3">
         <f>SUM(January:December!C36)</f>
-        <v>1203</v>
+        <v>1376</v>
       </c>
       <c r="D36" s="3">
         <f>SUM(January:December!D36)</f>
-        <v>6853</v>
+        <v>7713</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4026,15 +4026,15 @@
       </c>
       <c r="B37" s="4">
         <f>SUM(January:December!B37)</f>
-        <v>23812</v>
+        <v>27251</v>
       </c>
       <c r="C37" s="4">
         <f>SUM(January:December!C37)</f>
-        <v>4054</v>
+        <v>4651</v>
       </c>
       <c r="D37" s="4">
         <f>SUM(January:December!D37)</f>
-        <v>27866</v>
+        <v>31902</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4043,15 +4043,15 @@
       </c>
       <c r="B38" s="3">
         <f>SUM(January:December!B38)</f>
-        <v>2082</v>
+        <v>2246</v>
       </c>
       <c r="C38" s="3">
         <f>SUM(January:December!C38)</f>
-        <v>275</v>
+        <v>312</v>
       </c>
       <c r="D38" s="3">
         <f>SUM(January:December!D38)</f>
-        <v>2357</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4060,15 +4060,15 @@
       </c>
       <c r="B39" s="4">
         <f>SUM(January:December!B39)</f>
-        <v>735</v>
+        <v>791</v>
       </c>
       <c r="C39" s="4">
         <f>SUM(January:December!C39)</f>
-        <v>936</v>
+        <v>1022</v>
       </c>
       <c r="D39" s="4">
         <f>SUM(January:December!D39)</f>
-        <v>1671</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4077,15 +4077,15 @@
       </c>
       <c r="B40" s="7">
         <f>SUM(January:December!B40)</f>
-        <v>1934</v>
+        <v>2468</v>
       </c>
       <c r="C40" s="7">
         <f>SUM(January:December!C40)</f>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D40" s="7">
         <f>SUM(January:December!D40)</f>
-        <v>2009</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4094,15 +4094,15 @@
       </c>
       <c r="B41" s="8">
         <f>SUM(January:December!B41)</f>
-        <v>8521</v>
+        <v>10190</v>
       </c>
       <c r="C41" s="8">
         <f>SUM(January:December!C41)</f>
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D41" s="8">
         <f>SUM(January:December!D41)</f>
-        <v>8969</v>
+        <v>10640</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4111,15 +4111,15 @@
       </c>
       <c r="B42" s="7">
         <f>SUM(January:December!B42)</f>
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="C42" s="7">
         <f>SUM(January:December!C42)</f>
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D42" s="7">
         <f>SUM(January:December!D42)</f>
-        <v>174</v>
+        <v>217</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4128,15 +4128,15 @@
       </c>
       <c r="B43" s="8">
         <f>SUM(January:December!B43)</f>
-        <v>1086</v>
+        <v>1429</v>
       </c>
       <c r="C43" s="8">
         <f>SUM(January:December!C43)</f>
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D43" s="8">
         <f>SUM(January:December!D43)</f>
-        <v>1137</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4145,15 +4145,15 @@
       </c>
       <c r="B44" s="3">
         <f>SUM(January:December!B44)</f>
-        <v>2623</v>
+        <v>2818</v>
       </c>
       <c r="C44" s="3">
         <f>SUM(January:December!C44)</f>
-        <v>436</v>
+        <v>496</v>
       </c>
       <c r="D44" s="3">
         <f>SUM(January:December!D44)</f>
-        <v>3059</v>
+        <v>3314</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4162,15 +4162,15 @@
       </c>
       <c r="B45" s="4">
         <f>SUM(January:December!B45)</f>
-        <v>9678</v>
+        <v>11185</v>
       </c>
       <c r="C45" s="4">
         <f>SUM(January:December!C45)</f>
-        <v>3599</v>
+        <v>4188</v>
       </c>
       <c r="D45" s="4">
         <f>SUM(January:December!D45)</f>
-        <v>13277</v>
+        <v>15373</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4179,15 +4179,15 @@
       </c>
       <c r="B46" s="3">
         <f>SUM(January:December!B46)</f>
-        <v>23105</v>
+        <v>26024</v>
       </c>
       <c r="C46" s="3">
         <f>SUM(January:December!C46)</f>
-        <v>5887</v>
+        <v>6794</v>
       </c>
       <c r="D46" s="3">
         <f>SUM(January:December!D46)</f>
-        <v>28992</v>
+        <v>32818</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4196,15 +4196,15 @@
       </c>
       <c r="B47" s="4">
         <f>SUM(January:December!B47)</f>
-        <v>11269</v>
+        <v>12724</v>
       </c>
       <c r="C47" s="4">
         <f>SUM(January:December!C47)</f>
-        <v>1581</v>
+        <v>1802</v>
       </c>
       <c r="D47" s="4">
         <f>SUM(January:December!D47)</f>
-        <v>12850</v>
+        <v>14526</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4213,15 +4213,15 @@
       </c>
       <c r="B48" s="3">
         <f>SUM(January:December!B48)</f>
-        <v>3820</v>
+        <v>4583</v>
       </c>
       <c r="C48" s="3">
         <f>SUM(January:December!C48)</f>
-        <v>2673</v>
+        <v>3102</v>
       </c>
       <c r="D48" s="3">
         <f>SUM(January:December!D48)</f>
-        <v>6493</v>
+        <v>7685</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4230,15 +4230,15 @@
       </c>
       <c r="B49" s="4">
         <f>SUM(January:December!B49)</f>
-        <v>23548</v>
+        <v>26874</v>
       </c>
       <c r="C49" s="4">
         <f>SUM(January:December!C49)</f>
-        <v>6699</v>
+        <v>7616</v>
       </c>
       <c r="D49" s="4">
         <f>SUM(January:December!D49)</f>
-        <v>30247</v>
+        <v>34490</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4247,15 +4247,15 @@
       </c>
       <c r="B50" s="3">
         <f>SUM(January:December!B50)</f>
-        <v>2714</v>
+        <v>3035</v>
       </c>
       <c r="C50" s="3">
         <f>SUM(January:December!C50)</f>
-        <v>810</v>
+        <v>922</v>
       </c>
       <c r="D50" s="3">
         <f>SUM(January:December!D50)</f>
-        <v>3524</v>
+        <v>3957</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4264,15 +4264,15 @@
       </c>
       <c r="B51" s="4">
         <f>SUM(January:December!B51)</f>
-        <v>6234</v>
+        <v>6950</v>
       </c>
       <c r="C51" s="4">
         <f>SUM(January:December!C51)</f>
-        <v>2994</v>
+        <v>3369</v>
       </c>
       <c r="D51" s="4">
         <f>SUM(January:December!D51)</f>
-        <v>9228</v>
+        <v>10319</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4281,15 +4281,15 @@
       </c>
       <c r="B52" s="3">
         <f>SUM(January:December!B52)</f>
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="C52" s="3">
         <f>SUM(January:December!C52)</f>
-        <v>697</v>
+        <v>754</v>
       </c>
       <c r="D52" s="3">
         <f>SUM(January:December!D52)</f>
-        <v>1323</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4298,15 +4298,15 @@
       </c>
       <c r="B53" s="4">
         <f>SUM(January:December!B53)</f>
-        <v>1367</v>
+        <v>1490</v>
       </c>
       <c r="C53" s="4">
         <f>SUM(January:December!C53)</f>
-        <v>193</v>
+        <v>242</v>
       </c>
       <c r="D53" s="4">
         <f>SUM(January:December!D53)</f>
-        <v>1560</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4315,15 +4315,15 @@
       </c>
       <c r="B54" s="3">
         <f>SUM(January:December!B54)</f>
-        <v>2600</v>
+        <v>3013</v>
       </c>
       <c r="C54" s="3">
         <f>SUM(January:December!C54)</f>
-        <v>2688</v>
+        <v>3069</v>
       </c>
       <c r="D54" s="3">
         <f>SUM(January:December!D54)</f>
-        <v>5288</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4332,15 +4332,15 @@
       </c>
       <c r="B55" s="6">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>7363</v>
+        <v>8400</v>
       </c>
       <c r="C55" s="6">
         <f t="shared" ref="C55:D55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>1556</v>
+        <v>1748</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="0"/>
-        <v>8919</v>
+        <v>10148</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4349,15 +4349,15 @@
       </c>
       <c r="B56" s="8">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>11691</v>
+        <v>14272</v>
       </c>
       <c r="C56" s="8">
         <f t="shared" ref="C56:D56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="D56" s="8">
         <f t="shared" si="1"/>
-        <v>12289</v>
+        <v>14889</v>
       </c>
     </row>
   </sheetData>
@@ -9092,73 +9092,125 @@
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="B2" s="3">
+        <v>4404</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1469</v>
+      </c>
+      <c r="D2" s="3">
+        <v>5873</v>
+      </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="B3" s="4">
+        <v>2859</v>
+      </c>
+      <c r="C3" s="4">
+        <v>633</v>
+      </c>
+      <c r="D3" s="4">
+        <v>3492</v>
+      </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="B4" s="3">
+        <v>7685</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1232</v>
+      </c>
+      <c r="D4" s="3">
+        <v>8917</v>
+      </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="B5" s="4">
+        <v>148</v>
+      </c>
+      <c r="C5" s="4">
+        <v>31</v>
+      </c>
+      <c r="D5" s="4">
+        <v>179</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="B6" s="3">
+        <v>5246</v>
+      </c>
+      <c r="C6" s="3">
+        <v>907</v>
+      </c>
+      <c r="D6" s="3">
+        <v>6153</v>
+      </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="B7" s="4">
+        <v>625</v>
+      </c>
+      <c r="C7" s="4">
+        <v>256</v>
+      </c>
+      <c r="D7" s="4">
+        <v>881</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="B8" s="3">
+        <v>323</v>
+      </c>
+      <c r="C8" s="3">
+        <v>128</v>
+      </c>
+      <c r="D8" s="3">
+        <v>451</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="B9" s="4">
+        <v>282</v>
+      </c>
+      <c r="C9" s="4">
+        <v>94</v>
+      </c>
+      <c r="D9" s="4">
+        <v>376</v>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3"/>
+      <c r="B10" s="3">
+        <v>50</v>
+      </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="D10" s="3">
+        <v>50</v>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -9172,113 +9224,197 @@
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="B12" s="5">
+        <v>55</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5">
+        <v>57</v>
+      </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+      <c r="B13" s="6">
+        <v>161</v>
+      </c>
+      <c r="C13" s="6">
+        <v>26</v>
+      </c>
+      <c r="D13" s="6">
+        <v>187</v>
+      </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="B14" s="5">
+        <v>560</v>
+      </c>
+      <c r="C14" s="5">
+        <v>112</v>
+      </c>
+      <c r="D14" s="5">
+        <v>672</v>
+      </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="B15" s="6">
+        <v>261</v>
+      </c>
+      <c r="C15" s="6">
+        <v>52</v>
+      </c>
+      <c r="D15" s="6">
+        <v>313</v>
+      </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+      <c r="B16" s="3">
+        <v>271</v>
+      </c>
+      <c r="C16" s="3">
+        <v>57</v>
+      </c>
+      <c r="D16" s="3">
+        <v>328</v>
+      </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+      <c r="B17" s="4">
+        <v>1367</v>
+      </c>
+      <c r="C17" s="4">
+        <v>720</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2087</v>
+      </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+      <c r="B18" s="3">
+        <v>92</v>
+      </c>
+      <c r="C18" s="3">
+        <v>46</v>
+      </c>
+      <c r="D18" s="3">
+        <v>138</v>
+      </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
+      <c r="B19" s="4">
+        <v>1743</v>
+      </c>
+      <c r="C19" s="4">
+        <v>484</v>
+      </c>
+      <c r="D19" s="4">
+        <v>2227</v>
+      </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+      <c r="B20" s="3">
+        <v>35</v>
+      </c>
+      <c r="C20" s="3">
+        <v>5</v>
+      </c>
+      <c r="D20" s="3">
+        <v>40</v>
+      </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
+      <c r="B21" s="4">
+        <v>1711</v>
+      </c>
+      <c r="C21" s="4">
+        <v>495</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2206</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="B22" s="3">
+        <v>230</v>
+      </c>
+      <c r="C22" s="3">
+        <v>73</v>
+      </c>
+      <c r="D22" s="3">
+        <v>303</v>
+      </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="B23" s="4">
+        <v>2459</v>
+      </c>
+      <c r="C23" s="4">
+        <v>797</v>
+      </c>
+      <c r="D23" s="4">
+        <v>3256</v>
+      </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="B24" s="3">
+        <v>11939</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1765</v>
+      </c>
+      <c r="D24" s="3">
+        <v>13704</v>
+      </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
+      <c r="B25" s="4">
+        <v>595</v>
+      </c>
+      <c r="C25" s="4">
+        <v>160</v>
+      </c>
+      <c r="D25" s="4">
+        <v>755</v>
+      </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
@@ -9292,225 +9428,393 @@
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
+      <c r="B27" s="4">
+        <v>370</v>
+      </c>
+      <c r="C27" s="4">
+        <v>191</v>
+      </c>
+      <c r="D27" s="4">
+        <v>561</v>
+      </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="B28" s="3">
+        <v>293</v>
+      </c>
+      <c r="C28" s="3">
+        <v>183</v>
+      </c>
+      <c r="D28" s="3">
+        <v>476</v>
+      </c>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="B29" s="4">
+        <v>1467</v>
+      </c>
+      <c r="C29" s="4">
+        <v>714</v>
+      </c>
+      <c r="D29" s="4">
+        <v>2181</v>
+      </c>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="B30" s="3">
+        <v>16</v>
+      </c>
+      <c r="C30" s="3">
+        <v>36</v>
+      </c>
+      <c r="D30" s="3">
+        <v>52</v>
+      </c>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
+      <c r="B31" s="4">
+        <v>143</v>
+      </c>
+      <c r="C31" s="4">
+        <v>41</v>
+      </c>
+      <c r="D31" s="4">
+        <v>184</v>
+      </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
+      <c r="B32" s="3">
+        <v>1416</v>
+      </c>
+      <c r="C32" s="3">
+        <v>439</v>
+      </c>
+      <c r="D32" s="3">
+        <v>1855</v>
+      </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
+      <c r="B33" s="4">
+        <v>971</v>
+      </c>
+      <c r="C33" s="4">
+        <v>366</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1337</v>
+      </c>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
+      <c r="B34" s="3">
+        <v>593</v>
+      </c>
+      <c r="C34" s="3">
+        <v>178</v>
+      </c>
+      <c r="D34" s="3">
+        <v>771</v>
+      </c>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
+      <c r="B35" s="4">
+        <v>6058</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1218</v>
+      </c>
+      <c r="D35" s="4">
+        <v>7276</v>
+      </c>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
+      <c r="B36" s="3">
+        <v>687</v>
+      </c>
+      <c r="C36" s="3">
+        <v>173</v>
+      </c>
+      <c r="D36" s="3">
+        <v>860</v>
+      </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
+      <c r="B37" s="4">
+        <v>3439</v>
+      </c>
+      <c r="C37" s="4">
+        <v>597</v>
+      </c>
+      <c r="D37" s="4">
+        <v>4036</v>
+      </c>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
+      <c r="B38" s="3">
+        <v>164</v>
+      </c>
+      <c r="C38" s="3">
+        <v>37</v>
+      </c>
+      <c r="D38" s="3">
+        <v>201</v>
+      </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
+      <c r="B39" s="4">
+        <v>56</v>
+      </c>
+      <c r="C39" s="4">
+        <v>86</v>
+      </c>
+      <c r="D39" s="4">
+        <v>142</v>
+      </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
+      <c r="B40" s="7">
+        <v>534</v>
+      </c>
+      <c r="C40" s="7">
+        <v>4</v>
+      </c>
+      <c r="D40" s="7">
+        <v>538</v>
+      </c>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
+      <c r="B41" s="8">
+        <v>1669</v>
+      </c>
+      <c r="C41" s="8">
+        <v>2</v>
+      </c>
+      <c r="D41" s="8">
+        <v>1671</v>
+      </c>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
+      <c r="B42" s="7">
+        <v>35</v>
+      </c>
+      <c r="C42" s="7">
+        <v>8</v>
+      </c>
+      <c r="D42" s="7">
+        <v>43</v>
+      </c>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
+      <c r="B43" s="8">
+        <v>343</v>
+      </c>
+      <c r="C43" s="8">
+        <v>5</v>
+      </c>
+      <c r="D43" s="8">
+        <v>348</v>
+      </c>
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
+      <c r="B44" s="3">
+        <v>195</v>
+      </c>
+      <c r="C44" s="3">
+        <v>60</v>
+      </c>
+      <c r="D44" s="3">
+        <v>255</v>
+      </c>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
+      <c r="B45" s="4">
+        <v>1507</v>
+      </c>
+      <c r="C45" s="4">
+        <v>589</v>
+      </c>
+      <c r="D45" s="4">
+        <v>2096</v>
+      </c>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
+      <c r="B46" s="3">
+        <v>2919</v>
+      </c>
+      <c r="C46" s="3">
+        <v>907</v>
+      </c>
+      <c r="D46" s="3">
+        <v>3826</v>
+      </c>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
+      <c r="B47" s="4">
+        <v>1455</v>
+      </c>
+      <c r="C47" s="4">
+        <v>221</v>
+      </c>
+      <c r="D47" s="4">
+        <v>1676</v>
+      </c>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
+      <c r="B48" s="3">
+        <v>763</v>
+      </c>
+      <c r="C48" s="3">
+        <v>429</v>
+      </c>
+      <c r="D48" s="3">
+        <v>1192</v>
+      </c>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
+      <c r="B49" s="4">
+        <v>3326</v>
+      </c>
+      <c r="C49" s="4">
+        <v>917</v>
+      </c>
+      <c r="D49" s="4">
+        <v>4243</v>
+      </c>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
+      <c r="B50" s="3">
+        <v>321</v>
+      </c>
+      <c r="C50" s="3">
+        <v>112</v>
+      </c>
+      <c r="D50" s="3">
+        <v>433</v>
+      </c>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
+      <c r="B51" s="4">
+        <v>716</v>
+      </c>
+      <c r="C51" s="4">
+        <v>375</v>
+      </c>
+      <c r="D51" s="4">
+        <v>1091</v>
+      </c>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
+      <c r="B52" s="3">
+        <v>47</v>
+      </c>
+      <c r="C52" s="3">
+        <v>57</v>
+      </c>
+      <c r="D52" s="3">
+        <v>104</v>
+      </c>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
+      <c r="B53" s="4">
+        <v>123</v>
+      </c>
+      <c r="C53" s="4">
+        <v>49</v>
+      </c>
+      <c r="D53" s="4">
+        <v>172</v>
+      </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
+      <c r="B54" s="3">
+        <v>413</v>
+      </c>
+      <c r="C54" s="3">
+        <v>381</v>
+      </c>
+      <c r="D54" s="3">
+        <v>794</v>
+      </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
@@ -9518,15 +9822,15 @@
       </c>
       <c r="B55" s="6">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>0</v>
+        <v>1037</v>
       </c>
       <c r="C55" s="6">
         <f t="shared" ref="C55:D55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9535,15 +9839,15 @@
       </c>
       <c r="B56" s="8">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>0</v>
+        <v>2581</v>
       </c>
       <c r="C56" s="8">
         <f t="shared" ref="C56:D56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D56" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2600</v>
       </c>
     </row>
   </sheetData>

--- a/statistics_files/2026/2026_99_gc_sharing.xlsx
+++ b/statistics_files/2026/2026_99_gc_sharing.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Staff\Documents\GitHub\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F056BA-3D8E-41CA-8120-C25BC2EE406E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C806A9E-4B82-410E-A592-9D9B68FACFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January" sheetId="1" r:id="rId1"/>
@@ -1149,13 +1149,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>5663</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>3255</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>9155</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -1301,7 +1301,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>1898</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>2530</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>11305</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -1505,7 +1505,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>2580</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>6895</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>3290</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -1715,7 +1715,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>3565</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>3880</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -1941,13 +1941,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1969,7 +1969,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1977,7 +1977,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -1985,7 +1985,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1993,7 +1993,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -2001,7 +2001,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -2009,7 +2009,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -2017,7 +2017,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -2025,7 +2025,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -2033,7 +2033,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -2041,7 +2041,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -2049,7 +2049,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -2057,7 +2057,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -2065,7 +2065,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -2073,7 +2073,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -2081,7 +2081,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -2089,7 +2089,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -2097,7 +2097,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -2105,7 +2105,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -2113,7 +2113,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -2121,7 +2121,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -2129,7 +2129,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -2137,7 +2137,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -2145,7 +2145,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -2153,7 +2153,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -2161,7 +2161,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -2169,7 +2169,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -2177,7 +2177,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -2185,7 +2185,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -2193,7 +2193,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -2201,7 +2201,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -2209,7 +2209,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -2217,7 +2217,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -2225,7 +2225,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -2233,7 +2233,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -2241,7 +2241,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -2249,7 +2249,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -2257,7 +2257,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -2265,7 +2265,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -2273,7 +2273,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -2281,7 +2281,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -2289,7 +2289,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -2297,7 +2297,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -2305,7 +2305,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -2313,7 +2313,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -2321,7 +2321,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -2329,7 +2329,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -2337,7 +2337,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -2345,7 +2345,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -2353,7 +2353,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -2361,7 +2361,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -2369,7 +2369,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -2377,7 +2377,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -2385,7 +2385,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -2429,13 +2429,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2457,7 +2457,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -2465,7 +2465,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -2473,7 +2473,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -2481,7 +2481,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -2489,7 +2489,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -2497,7 +2497,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -2505,7 +2505,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -2513,7 +2513,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -2521,7 +2521,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -2529,7 +2529,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -2537,7 +2537,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -2545,7 +2545,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -2553,7 +2553,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -2561,7 +2561,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -2569,7 +2569,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -2577,7 +2577,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -2585,7 +2585,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -2593,7 +2593,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -2601,7 +2601,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -2609,7 +2609,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -2617,7 +2617,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -2625,7 +2625,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -2633,7 +2633,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -2641,7 +2641,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -2649,7 +2649,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -2657,7 +2657,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -2665,7 +2665,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -2673,7 +2673,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -2681,7 +2681,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -2689,7 +2689,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -2697,7 +2697,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -2705,7 +2705,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -2713,7 +2713,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -2721,7 +2721,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -2729,7 +2729,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -2737,7 +2737,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -2745,7 +2745,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -2753,7 +2753,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -2761,7 +2761,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -2769,7 +2769,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -2777,7 +2777,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -2785,7 +2785,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -2793,7 +2793,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -2801,7 +2801,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -2809,7 +2809,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -2817,7 +2817,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -2825,7 +2825,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -2833,7 +2833,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -2841,7 +2841,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -2849,7 +2849,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -2857,7 +2857,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -2865,7 +2865,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -2873,7 +2873,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -2917,13 +2917,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2945,7 +2945,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -2953,7 +2953,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -2961,7 +2961,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -2969,7 +2969,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -2977,7 +2977,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -2985,7 +2985,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -2993,7 +2993,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -3001,7 +3001,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -3009,7 +3009,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -3017,7 +3017,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -3025,7 +3025,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -3033,7 +3033,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -3041,7 +3041,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -3049,7 +3049,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -3057,7 +3057,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -3065,7 +3065,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -3073,7 +3073,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -3081,7 +3081,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -3089,7 +3089,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -3097,7 +3097,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -3105,7 +3105,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -3113,7 +3113,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -3121,7 +3121,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -3129,7 +3129,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -3137,7 +3137,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -3145,7 +3145,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -3153,7 +3153,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -3161,7 +3161,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -3169,7 +3169,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -3177,7 +3177,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -3185,7 +3185,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -3193,7 +3193,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -3201,7 +3201,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -3209,7 +3209,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -3217,7 +3217,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -3225,7 +3225,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -3233,7 +3233,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -3241,7 +3241,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -3249,7 +3249,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -3257,7 +3257,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -3265,7 +3265,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -3273,7 +3273,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -3281,7 +3281,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -3289,7 +3289,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -3297,7 +3297,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -3305,7 +3305,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -3313,7 +3313,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -3321,7 +3321,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -3329,7 +3329,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -3337,7 +3337,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -3345,7 +3345,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -3353,7 +3353,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -3361,7 +3361,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -3405,13 +3405,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3425,149 +3425,149 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3">
         <f>SUM(January:December!B2)</f>
-        <v>35781</v>
+        <v>40522</v>
       </c>
       <c r="C2" s="3">
         <f>SUM(January:December!C2)</f>
-        <v>11394</v>
+        <v>13021</v>
       </c>
       <c r="D2" s="3">
         <f>SUM(January:December!D2)</f>
-        <v>47175</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>53543</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="4">
         <f>SUM(January:December!B3)</f>
-        <v>22925</v>
+        <v>25507</v>
       </c>
       <c r="C3" s="4">
         <f>SUM(January:December!C3)</f>
-        <v>5123</v>
+        <v>5798</v>
       </c>
       <c r="D3" s="4">
         <f>SUM(January:December!D3)</f>
-        <v>28048</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>31305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="3">
         <f>SUM(January:December!B4)</f>
-        <v>62917</v>
+        <v>70267</v>
       </c>
       <c r="C4" s="3">
         <f>SUM(January:December!C4)</f>
-        <v>9569</v>
+        <v>10803</v>
       </c>
       <c r="D4" s="3">
         <f>SUM(January:December!D4)</f>
-        <v>72486</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>81070</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>SUM(January:December!B5)</f>
-        <v>1264</v>
+        <v>1345</v>
       </c>
       <c r="C5" s="4">
         <f>SUM(January:December!C5)</f>
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="D5" s="4">
         <f>SUM(January:December!D5)</f>
-        <v>1459</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="3">
         <f>SUM(January:December!B6)</f>
-        <v>44139</v>
+        <v>49125</v>
       </c>
       <c r="C6" s="3">
         <f>SUM(January:December!C6)</f>
-        <v>7768</v>
+        <v>8791</v>
       </c>
       <c r="D6" s="3">
         <f>SUM(January:December!D6)</f>
-        <v>51907</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>57916</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>SUM(January:December!B7)</f>
-        <v>4828</v>
+        <v>5690</v>
       </c>
       <c r="C7" s="4">
         <f>SUM(January:December!C7)</f>
-        <v>2028</v>
+        <v>2299</v>
       </c>
       <c r="D7" s="4">
         <f>SUM(January:December!D7)</f>
-        <v>6856</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7989</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="3">
         <f>SUM(January:December!B8)</f>
-        <v>3302</v>
+        <v>3658</v>
       </c>
       <c r="C8" s="3">
         <f>SUM(January:December!C8)</f>
-        <v>929</v>
+        <v>1058</v>
       </c>
       <c r="D8" s="3">
         <f>SUM(January:December!D8)</f>
-        <v>4231</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4716</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="4">
         <f>SUM(January:December!B9)</f>
-        <v>1979</v>
+        <v>2206</v>
       </c>
       <c r="C9" s="4">
         <f>SUM(January:December!C9)</f>
-        <v>514</v>
+        <v>569</v>
       </c>
       <c r="D9" s="4">
         <f>SUM(January:December!D9)</f>
-        <v>2493</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="3">
         <f>SUM(January:December!B10)</f>
-        <v>427</v>
+        <v>469</v>
       </c>
       <c r="C10" s="3">
         <f>SUM(January:December!C10)</f>
@@ -3575,10 +3575,10 @@
       </c>
       <c r="D10" s="3">
         <f>SUM(January:December!D10)</f>
-        <v>432</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -3595,245 +3595,245 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="5">
         <f>SUM(January:December!B12)</f>
-        <v>287</v>
+        <v>321</v>
       </c>
       <c r="C12" s="5">
         <f>SUM(January:December!C12)</f>
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D12" s="5">
         <f>SUM(January:December!D12)</f>
-        <v>328</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="6">
         <f>SUM(January:December!B13)</f>
-        <v>1082</v>
+        <v>1163</v>
       </c>
       <c r="C13" s="6">
         <f>SUM(January:December!C13)</f>
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="D13" s="6">
         <f>SUM(January:December!D13)</f>
-        <v>1431</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>4793</v>
+        <v>5381</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>979</v>
+        <v>1149</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>5772</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>6530</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="6">
         <f>SUM(January:December!B15)</f>
-        <v>2238</v>
+        <v>2424</v>
       </c>
       <c r="C15" s="6">
         <f>SUM(January:December!C15)</f>
-        <v>379</v>
+        <v>421</v>
       </c>
       <c r="D15" s="6">
         <f>SUM(January:December!D15)</f>
-        <v>2617</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B16" s="3">
         <f>SUM(January:December!B16)</f>
-        <v>1984</v>
+        <v>2238</v>
       </c>
       <c r="C16" s="3">
         <f>SUM(January:December!C16)</f>
-        <v>470</v>
+        <v>549</v>
       </c>
       <c r="D16" s="3">
         <f>SUM(January:December!D16)</f>
-        <v>2454</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2787</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>SUM(January:December!B17)</f>
-        <v>11430</v>
+        <v>12794</v>
       </c>
       <c r="C17" s="4">
         <f>SUM(January:December!C17)</f>
-        <v>5246</v>
+        <v>5911</v>
       </c>
       <c r="D17" s="4">
         <f>SUM(January:December!D17)</f>
-        <v>16676</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>18705</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3">
         <f>SUM(January:December!B18)</f>
-        <v>797</v>
+        <v>912</v>
       </c>
       <c r="C18" s="3">
         <f>SUM(January:December!C18)</f>
-        <v>641</v>
+        <v>725</v>
       </c>
       <c r="D18" s="3">
         <f>SUM(January:December!D18)</f>
-        <v>1438</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>SUM(January:December!B19)</f>
-        <v>13864</v>
+        <v>15711</v>
       </c>
       <c r="C19" s="4">
         <f>SUM(January:December!C19)</f>
-        <v>4034</v>
+        <v>4710</v>
       </c>
       <c r="D19" s="4">
         <f>SUM(January:December!D19)</f>
-        <v>17898</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>20421</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="3">
         <f>SUM(January:December!B20)</f>
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="C20" s="3">
         <f>SUM(January:December!C20)</f>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D20" s="3">
         <f>SUM(January:December!D20)</f>
-        <v>182</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="4">
         <f>SUM(January:December!B21)</f>
-        <v>12845</v>
+        <v>14482</v>
       </c>
       <c r="C21" s="4">
         <f>SUM(January:December!C21)</f>
-        <v>3976</v>
+        <v>4597</v>
       </c>
       <c r="D21" s="4">
         <f>SUM(January:December!D21)</f>
-        <v>16821</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19079</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B22" s="3">
         <f>SUM(January:December!B22)</f>
-        <v>2276</v>
+        <v>2593</v>
       </c>
       <c r="C22" s="3">
         <f>SUM(January:December!C22)</f>
-        <v>659</v>
+        <v>722</v>
       </c>
       <c r="D22" s="3">
         <f>SUM(January:December!D22)</f>
-        <v>2935</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3315</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="4">
         <f>SUM(January:December!B23)</f>
-        <v>18266</v>
+        <v>20287</v>
       </c>
       <c r="C23" s="4">
         <f>SUM(January:December!C23)</f>
-        <v>5286</v>
+        <v>6137</v>
       </c>
       <c r="D23" s="4">
         <f>SUM(January:December!D23)</f>
-        <v>23552</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26424</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B24" s="3">
         <f>SUM(January:December!B24)</f>
-        <v>86643</v>
+        <v>97713</v>
       </c>
       <c r="C24" s="3">
         <f>SUM(January:December!C24)</f>
-        <v>13971</v>
+        <v>15814</v>
       </c>
       <c r="D24" s="3">
         <f>SUM(January:December!D24)</f>
-        <v>100614</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>113527</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="4">
         <f>SUM(January:December!B25)</f>
-        <v>3747</v>
+        <v>4239</v>
       </c>
       <c r="C25" s="4">
         <f>SUM(January:December!C25)</f>
-        <v>1215</v>
+        <v>1370</v>
       </c>
       <c r="D25" s="4">
         <f>SUM(January:December!D25)</f>
-        <v>4962</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5609</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -3850,514 +3850,514 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B27" s="4">
         <f>SUM(January:December!B27)</f>
-        <v>3611</v>
+        <v>3909</v>
       </c>
       <c r="C27" s="4">
         <f>SUM(January:December!C27)</f>
-        <v>1639</v>
+        <v>1765</v>
       </c>
       <c r="D27" s="4">
         <f>SUM(January:December!D27)</f>
-        <v>5250</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5674</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B28" s="3">
         <f>SUM(January:December!B28)</f>
-        <v>2629</v>
+        <v>3123</v>
       </c>
       <c r="C28" s="3">
         <f>SUM(January:December!C28)</f>
-        <v>1235</v>
+        <v>1535</v>
       </c>
       <c r="D28" s="3">
         <f>SUM(January:December!D28)</f>
-        <v>3864</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4658</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B29" s="4">
         <f>SUM(January:December!B29)</f>
-        <v>16482</v>
+        <v>18246</v>
       </c>
       <c r="C29" s="4">
         <f>SUM(January:December!C29)</f>
-        <v>6567</v>
+        <v>7404</v>
       </c>
       <c r="D29" s="4">
         <f>SUM(January:December!D29)</f>
-        <v>23049</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25650</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B30" s="3">
         <f>SUM(January:December!B30)</f>
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C30" s="3">
         <f>SUM(January:December!C30)</f>
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="D30" s="3">
         <f>SUM(January:December!D30)</f>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B31" s="4">
         <f>SUM(January:December!B31)</f>
-        <v>2275</v>
+        <v>2470</v>
       </c>
       <c r="C31" s="4">
         <f>SUM(January:December!C31)</f>
-        <v>844</v>
+        <v>907</v>
       </c>
       <c r="D31" s="4">
         <f>SUM(January:December!D31)</f>
-        <v>3119</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3377</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B32" s="3">
         <f>SUM(January:December!B32)</f>
-        <v>10989</v>
+        <v>12384</v>
       </c>
       <c r="C32" s="3">
         <f>SUM(January:December!C32)</f>
-        <v>3264</v>
+        <v>3816</v>
       </c>
       <c r="D32" s="3">
         <f>SUM(January:December!D32)</f>
-        <v>14253</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B33" s="4">
         <f>SUM(January:December!B33)</f>
-        <v>7599</v>
+        <v>8416</v>
       </c>
       <c r="C33" s="4">
         <f>SUM(January:December!C33)</f>
-        <v>2785</v>
+        <v>3111</v>
       </c>
       <c r="D33" s="4">
         <f>SUM(January:December!D33)</f>
-        <v>10384</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11527</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B34" s="3">
         <f>SUM(January:December!B34)</f>
-        <v>4069</v>
+        <v>4206</v>
       </c>
       <c r="C34" s="3">
         <f>SUM(January:December!C34)</f>
-        <v>1375</v>
+        <v>1455</v>
       </c>
       <c r="D34" s="3">
         <f>SUM(January:December!D34)</f>
-        <v>5444</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5661</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B35" s="4">
         <f>SUM(January:December!B35)</f>
-        <v>45680</v>
+        <v>51422</v>
       </c>
       <c r="C35" s="4">
         <f>SUM(January:December!C35)</f>
-        <v>8164</v>
+        <v>9202</v>
       </c>
       <c r="D35" s="4">
         <f>SUM(January:December!D35)</f>
-        <v>53844</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>60624</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B36" s="3">
         <f>SUM(January:December!B36)</f>
-        <v>6337</v>
+        <v>6922</v>
       </c>
       <c r="C36" s="3">
         <f>SUM(January:December!C36)</f>
-        <v>1376</v>
+        <v>1525</v>
       </c>
       <c r="D36" s="3">
         <f>SUM(January:December!D36)</f>
-        <v>7713</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8447</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B37" s="4">
         <f>SUM(January:December!B37)</f>
-        <v>27251</v>
+        <v>30215</v>
       </c>
       <c r="C37" s="4">
         <f>SUM(January:December!C37)</f>
-        <v>4651</v>
+        <v>5244</v>
       </c>
       <c r="D37" s="4">
         <f>SUM(January:December!D37)</f>
-        <v>31902</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35459</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B38" s="3">
         <f>SUM(January:December!B38)</f>
-        <v>2246</v>
+        <v>2517</v>
       </c>
       <c r="C38" s="3">
         <f>SUM(January:December!C38)</f>
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="D38" s="3">
         <f>SUM(January:December!D38)</f>
-        <v>2558</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2861</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B39" s="4">
         <f>SUM(January:December!B39)</f>
-        <v>791</v>
+        <v>875</v>
       </c>
       <c r="C39" s="4">
         <f>SUM(January:December!C39)</f>
-        <v>1022</v>
+        <v>1185</v>
       </c>
       <c r="D39" s="4">
         <f>SUM(January:December!D39)</f>
-        <v>1813</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B40" s="7">
         <f>SUM(January:December!B40)</f>
-        <v>2468</v>
+        <v>3141</v>
       </c>
       <c r="C40" s="7">
         <f>SUM(January:December!C40)</f>
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D40" s="7">
         <f>SUM(January:December!D40)</f>
-        <v>2547</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3229</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
       <c r="B41" s="8">
         <f>SUM(January:December!B41)</f>
-        <v>10190</v>
+        <v>12298</v>
       </c>
       <c r="C41" s="8">
         <f>SUM(January:December!C41)</f>
-        <v>450</v>
+        <v>498</v>
       </c>
       <c r="D41" s="8">
         <f>SUM(January:December!D41)</f>
-        <v>10640</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>12796</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
       <c r="B42" s="7">
         <f>SUM(January:December!B42)</f>
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="C42" s="7">
         <f>SUM(January:December!C42)</f>
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D42" s="7">
         <f>SUM(January:December!D42)</f>
-        <v>217</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B43" s="8">
         <f>SUM(January:December!B43)</f>
-        <v>1429</v>
+        <v>1863</v>
       </c>
       <c r="C43" s="8">
         <f>SUM(January:December!C43)</f>
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D43" s="8">
         <f>SUM(January:December!D43)</f>
-        <v>1485</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B44" s="3">
         <f>SUM(January:December!B44)</f>
-        <v>2818</v>
+        <v>3000</v>
       </c>
       <c r="C44" s="3">
         <f>SUM(January:December!C44)</f>
-        <v>496</v>
+        <v>544</v>
       </c>
       <c r="D44" s="3">
         <f>SUM(January:December!D44)</f>
-        <v>3314</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3544</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
       <c r="B45" s="4">
         <f>SUM(January:December!B45)</f>
-        <v>11185</v>
+        <v>13253</v>
       </c>
       <c r="C45" s="4">
         <f>SUM(January:December!C45)</f>
-        <v>4188</v>
+        <v>4960</v>
       </c>
       <c r="D45" s="4">
         <f>SUM(January:December!D45)</f>
-        <v>15373</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>18213</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B46" s="3">
         <f>SUM(January:December!B46)</f>
-        <v>26024</v>
+        <v>29055</v>
       </c>
       <c r="C46" s="3">
         <f>SUM(January:December!C46)</f>
-        <v>6794</v>
+        <v>7594</v>
       </c>
       <c r="D46" s="3">
         <f>SUM(January:December!D46)</f>
-        <v>32818</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>36649</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
       <c r="B47" s="4">
         <f>SUM(January:December!B47)</f>
-        <v>12724</v>
+        <v>14184</v>
       </c>
       <c r="C47" s="4">
         <f>SUM(January:December!C47)</f>
-        <v>1802</v>
+        <v>2005</v>
       </c>
       <c r="D47" s="4">
         <f>SUM(January:December!D47)</f>
-        <v>14526</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16189</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B48" s="3">
         <f>SUM(January:December!B48)</f>
-        <v>4583</v>
+        <v>5334</v>
       </c>
       <c r="C48" s="3">
         <f>SUM(January:December!C48)</f>
-        <v>3102</v>
+        <v>3451</v>
       </c>
       <c r="D48" s="3">
         <f>SUM(January:December!D48)</f>
-        <v>7685</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8785</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B49" s="4">
         <f>SUM(January:December!B49)</f>
-        <v>26874</v>
+        <v>30008</v>
       </c>
       <c r="C49" s="4">
         <f>SUM(January:December!C49)</f>
-        <v>7616</v>
+        <v>8596</v>
       </c>
       <c r="D49" s="4">
         <f>SUM(January:December!D49)</f>
-        <v>34490</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>38604</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B50" s="3">
         <f>SUM(January:December!B50)</f>
-        <v>3035</v>
+        <v>3333</v>
       </c>
       <c r="C50" s="3">
         <f>SUM(January:December!C50)</f>
-        <v>922</v>
+        <v>1112</v>
       </c>
       <c r="D50" s="3">
         <f>SUM(January:December!D50)</f>
-        <v>3957</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4445</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B51" s="4">
         <f>SUM(January:December!B51)</f>
-        <v>6950</v>
+        <v>7638</v>
       </c>
       <c r="C51" s="4">
         <f>SUM(January:December!C51)</f>
-        <v>3369</v>
+        <v>3699</v>
       </c>
       <c r="D51" s="4">
         <f>SUM(January:December!D51)</f>
-        <v>10319</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11337</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B52" s="3">
         <f>SUM(January:December!B52)</f>
-        <v>673</v>
+        <v>817</v>
       </c>
       <c r="C52" s="3">
         <f>SUM(January:December!C52)</f>
-        <v>754</v>
+        <v>825</v>
       </c>
       <c r="D52" s="3">
         <f>SUM(January:December!D52)</f>
-        <v>1427</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
       <c r="B53" s="4">
         <f>SUM(January:December!B53)</f>
-        <v>1490</v>
+        <v>1686</v>
       </c>
       <c r="C53" s="4">
         <f>SUM(January:December!C53)</f>
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="D53" s="4">
         <f>SUM(January:December!D53)</f>
-        <v>1732</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B54" s="3">
         <f>SUM(January:December!B54)</f>
-        <v>3013</v>
+        <v>3339</v>
       </c>
       <c r="C54" s="3">
         <f>SUM(January:December!C54)</f>
-        <v>3069</v>
+        <v>3356</v>
       </c>
       <c r="D54" s="3">
         <f>SUM(January:December!D54)</f>
-        <v>6082</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>6695</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
       <c r="B55" s="6">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>8400</v>
+        <v>9289</v>
       </c>
       <c r="C55" s="6">
         <f t="shared" ref="C55:D55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>1748</v>
+        <v>2001</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="0"/>
-        <v>10148</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11290</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B56" s="8">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>14272</v>
+        <v>17516</v>
       </c>
       <c r="C56" s="8">
         <f t="shared" ref="C56:D56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>617</v>
+        <v>692</v>
       </c>
       <c r="D56" s="8">
         <f t="shared" si="1"/>
-        <v>14889</v>
+        <v>18208</v>
       </c>
     </row>
   </sheetData>
@@ -4370,13 +4370,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4390,7 +4390,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>5122</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>3066</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>8064</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -4460,7 +4460,7 @@
         <v>5650</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -4516,7 +4516,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -4524,7 +4524,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>10990</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -4728,7 +4728,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -4756,7 +4756,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>2376</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -4826,7 +4826,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>6409</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -4868,7 +4868,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -4882,7 +4882,7 @@
         <v>3292</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -4896,7 +4896,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -4924,7 +4924,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>2481</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>3081</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>3788</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -5106,7 +5106,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -5164,13 +5164,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>5840</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>3403</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>9487</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -5268,7 +5268,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -5282,7 +5282,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -5308,7 +5308,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -5316,7 +5316,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -5330,7 +5330,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -5358,7 +5358,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -5372,7 +5372,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -5386,7 +5386,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -5414,7 +5414,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -5428,7 +5428,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -5454,7 +5454,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>3233</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -5496,7 +5496,7 @@
         <v>12077</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -5510,7 +5510,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -5518,7 +5518,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -5532,7 +5532,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -5546,7 +5546,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -5574,7 +5574,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -5588,7 +5588,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -5616,7 +5616,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -5630,7 +5630,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>6076</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -5658,7 +5658,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>3854</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -5686,7 +5686,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -5700,7 +5700,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -5714,7 +5714,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -5728,7 +5728,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -5742,7 +5742,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -5770,7 +5770,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -5784,7 +5784,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -5798,7 +5798,7 @@
         <v>3539</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -5812,7 +5812,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -5826,7 +5826,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>4098</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -5854,7 +5854,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -5868,7 +5868,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -5882,7 +5882,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -5896,7 +5896,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -5927,7 +5927,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -5954,13 +5954,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5974,7 +5974,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>5254</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -6002,7 +6002,7 @@
         <v>2831</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -6016,7 +6016,7 @@
         <v>8105</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -6044,7 +6044,7 @@
         <v>5965</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -6058,7 +6058,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -6072,7 +6072,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -6086,7 +6086,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -6106,7 +6106,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -6134,7 +6134,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -6148,7 +6148,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -6162,7 +6162,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -6190,7 +6190,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -6204,7 +6204,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -6274,7 +6274,7 @@
         <v>2971</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>11327</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -6302,7 +6302,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -6310,7 +6310,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -6324,7 +6324,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -6338,7 +6338,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>2770</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -6366,7 +6366,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -6380,7 +6380,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -6394,7 +6394,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -6408,7 +6408,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -6422,7 +6422,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -6436,7 +6436,7 @@
         <v>3565</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -6450,7 +6450,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -6464,7 +6464,7 @@
         <v>3385</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -6478,7 +6478,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -6506,7 +6506,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -6534,7 +6534,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -6548,7 +6548,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -6562,7 +6562,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -6576,7 +6576,7 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -6590,7 +6590,7 @@
         <v>2919</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -6604,7 +6604,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -6618,7 +6618,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -6632,7 +6632,7 @@
         <v>3745</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -6646,7 +6646,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -6674,7 +6674,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -6688,7 +6688,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -6702,7 +6702,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -6719,7 +6719,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -6746,13 +6746,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6766,7 +6766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>5945</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -6794,7 +6794,7 @@
         <v>3615</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -6808,7 +6808,7 @@
         <v>8217</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -6822,7 +6822,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -6836,7 +6836,7 @@
         <v>6259</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -6850,7 +6850,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -6864,7 +6864,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -6878,7 +6878,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -6890,7 +6890,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -6898,7 +6898,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -6926,7 +6926,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -6940,7 +6940,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -6954,7 +6954,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -6968,7 +6968,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -6982,7 +6982,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -7010,7 +7010,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -7024,7 +7024,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -7038,7 +7038,7 @@
         <v>2128</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -7052,7 +7052,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -7066,7 +7066,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -7080,7 +7080,7 @@
         <v>13121</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -7094,7 +7094,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -7102,7 +7102,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -7116,7 +7116,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -7130,7 +7130,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -7144,7 +7144,7 @@
         <v>3173</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -7172,7 +7172,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -7186,7 +7186,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -7200,7 +7200,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -7214,7 +7214,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -7228,7 +7228,7 @@
         <v>5483</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -7242,7 +7242,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -7256,7 +7256,7 @@
         <v>4080</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -7270,7 +7270,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -7296,7 +7296,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -7310,7 +7310,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -7322,7 +7322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -7330,7 +7330,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -7344,7 +7344,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -7358,7 +7358,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -7372,7 +7372,7 @@
         <v>4979</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -7386,7 +7386,7 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -7400,7 +7400,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>4667</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -7428,7 +7428,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -7442,7 +7442,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -7456,7 +7456,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -7470,7 +7470,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -7484,7 +7484,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -7501,7 +7501,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -7528,13 +7528,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7548,7 +7548,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -7562,7 +7562,7 @@
         <v>6881</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -7576,7 +7576,7 @@
         <v>4172</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>10577</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -7604,7 +7604,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -7618,7 +7618,7 @@
         <v>7611</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -7632,7 +7632,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -7660,7 +7660,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -7672,7 +7672,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -7680,7 +7680,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -7694,7 +7694,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -7708,7 +7708,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -7736,7 +7736,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -7764,7 +7764,7 @@
         <v>2775</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -7778,7 +7778,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -7792,7 +7792,7 @@
         <v>2549</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -7806,7 +7806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -7820,7 +7820,7 @@
         <v>2395</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -7834,7 +7834,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>3458</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -7862,7 +7862,7 @@
         <v>14023</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -7876,7 +7876,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -7884,7 +7884,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -7898,7 +7898,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -7912,7 +7912,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -7926,7 +7926,7 @@
         <v>3982</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -7940,7 +7940,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -7968,7 +7968,7 @@
         <v>2172</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -7982,7 +7982,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -7996,7 +7996,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -8010,7 +8010,7 @@
         <v>9813</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -8024,7 +8024,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -8038,7 +8038,7 @@
         <v>5094</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -8066,7 +8066,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -8074,7 +8074,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -8082,7 +8082,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -8094,7 +8094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -8102,7 +8102,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -8116,7 +8116,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -8144,7 +8144,7 @@
         <v>6162</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -8158,7 +8158,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -8172,7 +8172,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -8186,7 +8186,7 @@
         <v>5410</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -8200,7 +8200,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -8214,7 +8214,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -8228,7 +8228,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -8242,7 +8242,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -8256,7 +8256,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -8300,13 +8300,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8320,7 +8320,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -8334,7 +8334,7 @@
         <v>6597</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -8348,7 +8348,7 @@
         <v>4214</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -8362,7 +8362,7 @@
         <v>9964</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -8376,7 +8376,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -8390,7 +8390,7 @@
         <v>7707</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -8404,7 +8404,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -8432,7 +8432,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -8446,7 +8446,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -8454,7 +8454,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -8468,7 +8468,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -8482,7 +8482,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -8496,7 +8496,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -8510,7 +8510,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -8524,7 +8524,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -8538,7 +8538,7 @@
         <v>2466</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -8552,7 +8552,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -8566,7 +8566,7 @@
         <v>2679</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -8578,7 +8578,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -8592,7 +8592,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -8606,7 +8606,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -8620,7 +8620,7 @@
         <v>3745</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -8634,7 +8634,7 @@
         <v>14067</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -8648,7 +8648,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -8656,7 +8656,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -8684,7 +8684,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -8698,7 +8698,7 @@
         <v>3439</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -8712,7 +8712,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -8726,7 +8726,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -8740,7 +8740,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -8754,7 +8754,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -8768,7 +8768,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -8782,7 +8782,7 @@
         <v>8327</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -8796,7 +8796,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -8810,7 +8810,7 @@
         <v>4871</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -8824,7 +8824,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -8838,7 +8838,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -8846,7 +8846,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -8854,7 +8854,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -8862,7 +8862,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -8870,7 +8870,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -8884,7 +8884,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -8898,7 +8898,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -8912,7 +8912,7 @@
         <v>4747</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -8926,7 +8926,7 @@
         <v>2436</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -8940,7 +8940,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -8954,7 +8954,7 @@
         <v>4659</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -8968,7 +8968,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -8982,7 +8982,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -8996,7 +8996,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -9010,7 +9010,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -9024,7 +9024,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -9041,7 +9041,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -9068,13 +9068,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -9102,7 +9102,7 @@
         <v>5873</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -9116,7 +9116,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -9130,7 +9130,7 @@
         <v>8917</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -9144,7 +9144,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -9158,7 +9158,7 @@
         <v>6153</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -9172,7 +9172,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -9186,7 +9186,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -9200,7 +9200,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -9212,7 +9212,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -9220,7 +9220,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -9234,7 +9234,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -9248,7 +9248,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -9262,7 +9262,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -9290,7 +9290,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -9304,7 +9304,7 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -9332,7 +9332,7 @@
         <v>2227</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -9346,7 +9346,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -9360,7 +9360,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -9374,7 +9374,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -9388,7 +9388,7 @@
         <v>3256</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>13704</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -9416,7 +9416,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -9424,7 +9424,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -9452,7 +9452,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -9466,7 +9466,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -9480,7 +9480,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -9494,7 +9494,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -9508,7 +9508,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -9522,7 +9522,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -9536,7 +9536,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -9550,7 +9550,7 @@
         <v>7276</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -9578,7 +9578,7 @@
         <v>4036</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -9592,7 +9592,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -9606,7 +9606,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -9620,7 +9620,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -9634,7 +9634,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -9648,7 +9648,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -9662,7 +9662,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -9676,7 +9676,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -9690,7 +9690,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -9704,7 +9704,7 @@
         <v>3826</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -9718,7 +9718,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -9732,7 +9732,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -9746,7 +9746,7 @@
         <v>4243</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -9760,7 +9760,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -9774,7 +9774,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -9788,7 +9788,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -9802,7 +9802,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -9833,7 +9833,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -9860,13 +9860,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9880,79 +9880,131 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="3">
+        <v>4741</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1627</v>
+      </c>
+      <c r="D2" s="3">
+        <v>6368</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
+        <v>2582</v>
+      </c>
+      <c r="C3" s="4">
+        <v>675</v>
+      </c>
+      <c r="D3" s="4">
+        <v>3257</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="3">
+        <v>7350</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1234</v>
+      </c>
+      <c r="D4" s="3">
+        <v>8584</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4">
+        <v>81</v>
+      </c>
+      <c r="C5" s="4">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="3">
+        <v>4986</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1023</v>
+      </c>
+      <c r="D6" s="3">
+        <v>6009</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4">
+        <v>862</v>
+      </c>
+      <c r="C7" s="4">
+        <v>271</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="3">
+        <v>356</v>
+      </c>
+      <c r="C8" s="3">
+        <v>129</v>
+      </c>
+      <c r="D8" s="3">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
+        <v>227</v>
+      </c>
+      <c r="C9" s="4">
+        <v>55</v>
+      </c>
+      <c r="D9" s="4">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3"/>
+      <c r="B10" s="3">
+        <v>42</v>
+      </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D10" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -9960,119 +10012,203 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="5">
+        <v>34</v>
+      </c>
+      <c r="C12" s="5">
+        <v>12</v>
+      </c>
+      <c r="D12" s="5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="6">
+        <v>81</v>
+      </c>
+      <c r="C13" s="6">
+        <v>29</v>
+      </c>
+      <c r="D13" s="6">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="5">
+        <v>588</v>
+      </c>
+      <c r="C14" s="5">
+        <v>170</v>
+      </c>
+      <c r="D14" s="5">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="6">
+        <v>186</v>
+      </c>
+      <c r="C15" s="6">
+        <v>42</v>
+      </c>
+      <c r="D15" s="6">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="3">
+        <v>254</v>
+      </c>
+      <c r="C16" s="3">
+        <v>79</v>
+      </c>
+      <c r="D16" s="3">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="4">
+        <v>1364</v>
+      </c>
+      <c r="C17" s="4">
+        <v>665</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="3">
+        <v>115</v>
+      </c>
+      <c r="C18" s="3">
+        <v>84</v>
+      </c>
+      <c r="D18" s="3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="4">
+        <v>1847</v>
+      </c>
+      <c r="C19" s="4">
+        <v>676</v>
+      </c>
+      <c r="D19" s="4">
+        <v>2523</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3">
+        <v>39</v>
+      </c>
+      <c r="C20" s="3">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="4">
+        <v>1637</v>
+      </c>
+      <c r="C21" s="4">
+        <v>621</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="3">
+        <v>317</v>
+      </c>
+      <c r="C22" s="3">
+        <v>63</v>
+      </c>
+      <c r="D22" s="3">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="4">
+        <v>2021</v>
+      </c>
+      <c r="C23" s="4">
+        <v>851</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="3">
+        <v>11070</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1843</v>
+      </c>
+      <c r="D24" s="3">
+        <v>12913</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="4">
+        <v>492</v>
+      </c>
+      <c r="C25" s="4">
+        <v>155</v>
+      </c>
+      <c r="D25" s="4">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -10080,262 +10216,430 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="4">
+        <v>298</v>
+      </c>
+      <c r="C27" s="4">
+        <v>126</v>
+      </c>
+      <c r="D27" s="4">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="3">
+        <v>494</v>
+      </c>
+      <c r="C28" s="3">
+        <v>300</v>
+      </c>
+      <c r="D28" s="3">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="4">
+        <v>1764</v>
+      </c>
+      <c r="C29" s="4">
+        <v>837</v>
+      </c>
+      <c r="D29" s="4">
+        <v>2601</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-    </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="3">
+        <v>18</v>
+      </c>
+      <c r="C30" s="3">
+        <v>22</v>
+      </c>
+      <c r="D30" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="4">
+        <v>195</v>
+      </c>
+      <c r="C31" s="4">
+        <v>63</v>
+      </c>
+      <c r="D31" s="4">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-    </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="3">
+        <v>1395</v>
+      </c>
+      <c r="C32" s="3">
+        <v>552</v>
+      </c>
+      <c r="D32" s="3">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-    </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="4">
+        <v>817</v>
+      </c>
+      <c r="C33" s="4">
+        <v>326</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-    </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="3">
+        <v>137</v>
+      </c>
+      <c r="C34" s="3">
+        <v>80</v>
+      </c>
+      <c r="D34" s="3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-    </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="4">
+        <v>5742</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1038</v>
+      </c>
+      <c r="D35" s="4">
+        <v>6780</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-    </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="3">
+        <v>585</v>
+      </c>
+      <c r="C36" s="3">
+        <v>149</v>
+      </c>
+      <c r="D36" s="3">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-    </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="4">
+        <v>2964</v>
+      </c>
+      <c r="C37" s="4">
+        <v>593</v>
+      </c>
+      <c r="D37" s="4">
+        <v>3557</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-    </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="3">
+        <v>271</v>
+      </c>
+      <c r="C38" s="3">
+        <v>32</v>
+      </c>
+      <c r="D38" s="3">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-    </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="4">
+        <v>84</v>
+      </c>
+      <c r="C39" s="4">
+        <v>163</v>
+      </c>
+      <c r="D39" s="4">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-    </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="7">
+        <v>673</v>
+      </c>
+      <c r="C40" s="7">
+        <v>9</v>
+      </c>
+      <c r="D40" s="7">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-    </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="8">
+        <v>2108</v>
+      </c>
+      <c r="C41" s="8">
+        <v>48</v>
+      </c>
+      <c r="D41" s="8">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-    </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="7">
+        <v>29</v>
+      </c>
+      <c r="C42" s="7">
+        <v>8</v>
+      </c>
+      <c r="D42" s="7">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-    </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="8">
+        <v>434</v>
+      </c>
+      <c r="C43" s="8">
+        <v>10</v>
+      </c>
+      <c r="D43" s="8">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-    </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="3">
+        <v>182</v>
+      </c>
+      <c r="C44" s="3">
+        <v>48</v>
+      </c>
+      <c r="D44" s="3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="4">
+        <v>2068</v>
+      </c>
+      <c r="C45" s="4">
+        <v>772</v>
+      </c>
+      <c r="D45" s="4">
+        <v>2840</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-    </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="3">
+        <v>3031</v>
+      </c>
+      <c r="C46" s="3">
+        <v>800</v>
+      </c>
+      <c r="D46" s="3">
+        <v>3831</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="4">
+        <v>1460</v>
+      </c>
+      <c r="C47" s="4">
+        <v>203</v>
+      </c>
+      <c r="D47" s="4">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-    </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="3">
+        <v>751</v>
+      </c>
+      <c r="C48" s="3">
+        <v>349</v>
+      </c>
+      <c r="D48" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-    </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="4">
+        <v>3134</v>
+      </c>
+      <c r="C49" s="4">
+        <v>980</v>
+      </c>
+      <c r="D49" s="4">
+        <v>4114</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-    </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="3">
+        <v>298</v>
+      </c>
+      <c r="C50" s="3">
+        <v>190</v>
+      </c>
+      <c r="D50" s="3">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-    </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="4">
+        <v>688</v>
+      </c>
+      <c r="C51" s="4">
+        <v>330</v>
+      </c>
+      <c r="D51" s="4">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-    </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="3">
+        <v>144</v>
+      </c>
+      <c r="C52" s="3">
+        <v>71</v>
+      </c>
+      <c r="D52" s="3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-    </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="4">
+        <v>196</v>
+      </c>
+      <c r="C53" s="4">
+        <v>30</v>
+      </c>
+      <c r="D53" s="4">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-    </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="3">
+        <v>326</v>
+      </c>
+      <c r="C54" s="3">
+        <v>287</v>
+      </c>
+      <c r="D54" s="3">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
       <c r="B55" s="6">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="C55" s="6">
         <f t="shared" ref="C55:D55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B56" s="8">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>0</v>
+        <v>3244</v>
       </c>
       <c r="C56" s="8">
         <f t="shared" ref="C56:D56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D56" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3319</v>
       </c>
     </row>
   </sheetData>
